--- a/Capítulo02/Capítulo02/META DE VENDAS.xlsx
+++ b/Capítulo02/Capítulo02/META DE VENDAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silvia\Documents\Livro Excel 2019\Avançado\Excel 2019\Planilhas\DO CURSO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo02/Capítulo02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1218D496-9041-4389-8CC2-314F5C26C686}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{1218D496-9041-4389-8CC2-314F5C26C686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2F5E732-F9B3-44AC-A6E4-8EC327B77727}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" xr2:uid="{C2251AFD-7915-41E2-8195-09761E75898C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C2251AFD-7915-41E2-8195-09761E75898C}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -23,15 +23,42 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Vendedor</t>
   </si>
@@ -61,6 +88,12 @@
   </si>
   <si>
     <t>Augusto</t>
+  </si>
+  <si>
+    <t>FUNÇÕES</t>
+  </si>
+  <si>
+    <t>#=SES(B4&gt;$B$1;"Ótimo";B4=$B$1;"Bom";B4&lt;$B$1;"Melhorar")</t>
   </si>
 </sst>
 </file>
@@ -70,7 +103,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,8 +140,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -118,6 +159,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -135,7 +188,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -144,6 +197,11 @@
     <xf numFmtId="44" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -163,9 +221,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -203,7 +261,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -309,7 +367,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -451,7 +509,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -459,15 +517,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8CE914-5E43-46CB-8AE3-9A9563BF5D02}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -475,7 +534,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -485,60 +544,84 @@
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="H3" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="7">
         <v>5200</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="9" t="str" cm="1">
+        <f t="array" ref="C4">_xlfn.IFS(B4&gt;$B$1,"Ótimo",B4=$B$1,"Bom",B4&lt;$B$1,"Melhorar")</f>
+        <v>Melhorar</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="7">
         <v>19000</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="6" t="str" cm="1">
+        <f t="array" ref="C5">_xlfn.IFS(B5&gt;$B$1,"Ótimo",B5=$B$1,"Bom",B5&lt;$B$1,"Melhorar")</f>
+        <v>Melhorar</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="7">
         <v>23000</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="6" t="str" cm="1">
+        <f t="array" ref="C6">_xlfn.IFS(B6&gt;$B$1,"Ótimo",B6=$B$1,"Bom",B6&lt;$B$1,"Melhorar")</f>
+        <v>Ótimo</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="7">
         <v>20000</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="6" t="str" cm="1">
+        <f t="array" ref="C7">_xlfn.IFS(B7&gt;$B$1,"Ótimo",B7=$B$1,"Bom",B7&lt;$B$1,"Melhorar")</f>
+        <v>Bom</v>
+      </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="7">
         <v>3500</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6" t="str" cm="1">
+        <f t="array" ref="C8">_xlfn.IFS(B8&gt;$B$1,"Ótimo",B8=$B$1,"Bom",B8&lt;$B$1,"Melhorar")</f>
+        <v>Melhorar</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7">
         <v>5600</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="6" t="str" cm="1">
+        <f t="array" ref="C9">_xlfn.IFS(B9&gt;$B$1,"Ótimo",B9=$B$1,"Bom",B9&lt;$B$1,"Melhorar")</f>
+        <v>Melhorar</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -547,6 +630,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -660,15 +752,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -676,13 +759,34 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A72BC17-872C-486E-8B4C-B7E71A1C635C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCA99C-3F93-4C28-A21D-09D66FE167DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCA99C-3F93-4C28-A21D-09D66FE167DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A72BC17-872C-486E-8B4C-B7E71A1C635C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE820C5E-5788-4B8E-945F-2E8C89BEA65F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE820C5E-5788-4B8E-945F-2E8C89BEA65F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>